--- a/concessao_BID_capital_giro.xlsx
+++ b/concessao_BID_capital_giro.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="123820"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sicoob-my.sharepoint.com/personal/caua_paniagua_sicoob_com_br/Documents/Teste/Ferramenta de Precificação (teste)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sicoob-my.sharepoint.com/personal/caua_paniagua_sicoob_com_br/Documents/Streamlit - Comercial de Crédito e Serviços/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_1F6C0890C0BCFE94BCE23D9FE6F854A268D2C6FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D88CDE7-2D5E-4662-B7CB-CB32850EED9A}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_1F6C0890C0BCFE94BCE23D9FE6F854A268D2C6FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B33544A-E3E0-431A-B02A-A9F1737627AC}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-620" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="page" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="252">
   <si>
     <t>Ano Movimento</t>
   </si>
@@ -771,6 +771,15 @@
   </si>
   <si>
     <t>44061422</t>
+  </si>
+  <si>
+    <t>44806772</t>
+  </si>
+  <si>
+    <t>44625654</t>
+  </si>
+  <si>
+    <t>44805907</t>
   </si>
 </sst>
 </file>
@@ -810,13 +819,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1118,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q177"/>
+  <dimension ref="A1:Q180"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -10521,6 +10535,165 @@
         <v>268564932402</v>
       </c>
     </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A178" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46113</v>
+      </c>
+      <c r="C178" s="7">
+        <v>2009</v>
+      </c>
+      <c r="D178" s="7">
+        <v>4370</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G178" s="7">
+        <v>-2</v>
+      </c>
+      <c r="H178" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I178" s="7">
+        <v>145358</v>
+      </c>
+      <c r="J178" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K178" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L178" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M178" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N178" s="9">
+        <v>108800</v>
+      </c>
+      <c r="O178" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P178" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q178" s="7">
+        <v>261737042703</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A179" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46111</v>
+      </c>
+      <c r="C179" s="7">
+        <v>1003</v>
+      </c>
+      <c r="D179" s="7">
+        <v>3172</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G179" s="7">
+        <v>-2</v>
+      </c>
+      <c r="H179" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I179" s="7">
+        <v>145356</v>
+      </c>
+      <c r="J179" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K179" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="L179" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M179" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N179" s="9">
+        <v>13920</v>
+      </c>
+      <c r="O179" s="10">
+        <v>1.17</v>
+      </c>
+      <c r="P179" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q179" s="7">
+        <v>266895102003</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A180" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B180" s="8">
+        <v>46113</v>
+      </c>
+      <c r="C180" s="7">
+        <v>2009</v>
+      </c>
+      <c r="D180" s="7">
+        <v>4370</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G180" s="7">
+        <v>-2</v>
+      </c>
+      <c r="H180" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I180" s="7">
+        <v>145356</v>
+      </c>
+      <c r="J180" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K180" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="L180" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M180" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N180" s="9">
+        <v>36000</v>
+      </c>
+      <c r="O180" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="P180" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q180" s="7">
+        <v>261686412703</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q165" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
